--- a/data/trans_bre/P32B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,58</t>
+          <t>-2,92; -0,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,66</t>
+          <t>-4,6; -0,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,56</t>
+          <t>-4,19; 0,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -0,88</t>
+          <t>-7,49; -0,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 112,29</t>
+          <t>-100,0; 46,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,66</t>
+          <t>-100,0; 103,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,67</t>
+          <t>-100,0; 27,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,01</t>
+          <t>-0,3; 2,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,73</t>
+          <t>-3,22; -0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,27</t>
+          <t>-1,9; 0,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,66</t>
+          <t>-1,65; 1,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,67; 447,49</t>
+          <t>-41,98; 501,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,5; -20,16</t>
+          <t>-86,72; -17,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 31,74</t>
+          <t>-76,11; 27,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,16; 254,0</t>
+          <t>-74,66; 210,08</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,13</t>
+          <t>-0,73; 3,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -1,17</t>
+          <t>-5,73; -1,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,63</t>
+          <t>-2,93; 0,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,38</t>
+          <t>-2,23; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,3</t>
+          <t>-100,0; 158,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,99; 152,32</t>
+          <t>-79,75; 147,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,13</t>
+          <t>-0,46; 1,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -1,27</t>
+          <t>-3,11; -1,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; -0,25</t>
+          <t>-1,98; -0,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,46</t>
+          <t>-1,87; 0,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 229,68</t>
+          <t>-46,95; 198,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,95; -51,26</t>
+          <t>-90,43; -44,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,41; -11,57</t>
+          <t>-77,55; -8,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 29,81</t>
+          <t>-72,61; 31,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-3,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-74,33%</t>
+          <t>-76,04%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; -0,58</t>
+          <t>-3,18; -0,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,57</t>
+          <t>-4,33; -0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,8</t>
+          <t>-4,24; 0,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -0,66</t>
+          <t>-7,14; -0,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 46,75</t>
+          <t>-100,0; 42,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,86</t>
+          <t>-100,0; 212,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,26</t>
+          <t>-100,0; -2,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,02</t>
+          <t>-0,24; 2,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,64</t>
+          <t>-3,22; -0,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,31</t>
+          <t>-1,97; 0,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,62</t>
+          <t>-0,72; 2,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 501,41</t>
+          <t>-39,3; 519,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,72; -17,36</t>
+          <t>-87,49; -23,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 27,67</t>
+          <t>-79,29; 16,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,66; 210,08</t>
+          <t>-44,24; 320,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-21,36%</t>
+          <t>-26,17%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,15</t>
+          <t>-0,42; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,14</t>
+          <t>-5,39; -1,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,84</t>
+          <t>-3,03; 0,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,22</t>
+          <t>-2,84; 1,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 158,19</t>
+          <t>-100,0; 111,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 147,32</t>
+          <t>-78,74; 132,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-32,75%</t>
+          <t>-12,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,11</t>
+          <t>-0,49; 1,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -1,18</t>
+          <t>-3,17; -1,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,98; -0,25</t>
+          <t>-1,97; -0,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,48</t>
+          <t>-1,52; 1,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 198,62</t>
+          <t>-48,24; 199,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,43; -44,3</t>
+          <t>-89,68; -45,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,55; -8,98</t>
+          <t>-74,7; -5,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 31,9</t>
+          <t>-55,37; 58,55</t>
         </is>
       </c>
     </row>
